--- a/Model_Comparison_Across_Networks.xlsx
+++ b/Model_Comparison_Across_Networks.xlsx
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>96.29276648999999</v>
+        <v>71.59054244000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>257.45491336</v>
+        <v>105.43504684</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>253.32733174</v>
+        <v>109.94782728</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>324.1954926</v>
+        <v>116.94121104</v>
       </c>
     </row>
     <row r="3">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>91.06428000000001</v>
+        <v>91.67654</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>80.72744</v>
+        <v>78.01594</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>80.78848000000001</v>
+        <v>78.28578</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>87.78019999999999</v>
+        <v>96.2818</v>
       </c>
     </row>
     <row r="4">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>205.16541334</v>
+        <v>171.06750906</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>205.94537886</v>
+        <v>213.9586902200001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>209.38599</v>
+        <v>255.16770582</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>198.14512226</v>
+        <v>212.66504392</v>
       </c>
     </row>
     <row r="5">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>91.52605</v>
+        <v>90.72194</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>68.84842</v>
+        <v>78.11203999999999</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>72.40596000000001</v>
+        <v>77.50592</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>93.32698000000001</v>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>929.10379094</v>
+        <v>887.45526874</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>402.43794206</v>
+        <v>611.75803042</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>398.94096058</v>
+        <v>608.3930804399999</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>439.5389236</v>
+        <v>514.5637450400001</v>
       </c>
     </row>
     <row r="7">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>84.09765999999999</v>
+        <v>82.45252000000001</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>77.25902000000001</v>
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>779.32355682</v>
+        <v>678.0726331799999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>380.1999963600001</v>
+        <v>725.6329613599999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>379.02569662</v>
+        <v>733.6272137800001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>387.99922672</v>
+        <v>711.6739775000001</v>
       </c>
     </row>
     <row r="9">
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>87.72114999999999</v>
+        <v>87.71088</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>73.35805999999999</v>
+        <v>77.61855999999999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>73.12326</v>
+        <v>77.50183999999999</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>73.89806000000002</v>
+        <v>94.87696</v>
       </c>
     </row>
   </sheetData>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>502.4713818975</v>
+        <v>452.046488355</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>311.50955766</v>
+        <v>414.19618221</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>310.169994735</v>
+        <v>426.78395683</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>337.469691295</v>
+        <v>388.960994375</v>
       </c>
     </row>
     <row r="3">
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>88.60228499999999</v>
+        <v>88.14047000000001</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>75.04823500000001</v>
+        <v>77.75139</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>75.792355</v>
+        <v>77.536315</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>85.77330500000001</v>
+        <v>93.14343</v>
       </c>
     </row>
   </sheetData>
@@ -948,25 +948,25 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>96.29276648999999</v>
+        <v>71.59054244000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>324.1954926</v>
+        <v>116.94121104</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>-227.90272611</v>
+        <v>-45.35066859999999</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>-236.6768911283359</v>
+        <v>-63.3472900949289</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>91.06428000000001</v>
+        <v>91.67654</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>87.78019999999999</v>
+        <v>96.2818</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>-3.284080000000017</v>
+        <v>4.605260000000001</v>
       </c>
     </row>
     <row r="3">
@@ -978,25 +978,25 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>257.45491336</v>
+        <v>105.43504684</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>324.1954926</v>
+        <v>116.94121104</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>-66.74057924000002</v>
+        <v>-11.50616419999998</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-25.92321054159742</v>
+        <v>-10.91303560329502</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>80.72744</v>
+        <v>78.01594</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>87.78019999999999</v>
+        <v>96.2818</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>7.052759999999992</v>
+        <v>18.26586</v>
       </c>
     </row>
     <row r="4">
@@ -1008,25 +1008,25 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>253.32733174</v>
+        <v>109.94782728</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>324.1954926</v>
+        <v>116.94121104</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>-70.86816086</v>
+        <v>-6.993383759999997</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-27.97493676392362</v>
+        <v>-6.360638434618821</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>80.78848000000001</v>
+        <v>78.28578</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>87.78019999999999</v>
+        <v>96.2818</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>6.991719999999987</v>
+        <v>17.99602</v>
       </c>
     </row>
     <row r="5">
@@ -1046,25 +1046,25 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>205.16541334</v>
+        <v>171.06750906</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>198.14512226</v>
+        <v>212.66504392</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>7.020291079999966</v>
+        <v>-41.59753486000002</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3.421771226306037</v>
+        <v>-24.31644389315925</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>91.52605</v>
+        <v>90.72194</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>93.32698000000001</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>1.800930000000008</v>
+        <v>2.605040000000002</v>
       </c>
     </row>
     <row r="6">
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>205.94537886</v>
+        <v>213.9586902200001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>198.14512226</v>
+        <v>212.66504392</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>7.800256599999994</v>
+        <v>1.293646300000022</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>3.787536599839195</v>
+        <v>0.6046243312995833</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>68.84842</v>
+        <v>78.11203999999999</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>93.32698000000001</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>24.47856</v>
+        <v>15.21494000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1106,25 +1106,25 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>209.38599</v>
+        <v>255.16770582</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>198.14512226</v>
+        <v>212.66504392</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>11.24086773999999</v>
+        <v>42.50266189999995</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>5.368490862258735</v>
+        <v>16.65675590232493</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>72.40596000000001</v>
+        <v>77.50592</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>93.32698000000001</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>20.92102</v>
+        <v>15.82106</v>
       </c>
     </row>
     <row r="8">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>929.10379094</v>
+        <v>887.45526874</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>439.5389236</v>
+        <v>514.5637450400001</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>489.56486734</v>
+        <v>372.8915236999999</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>52.6921612110412</v>
+        <v>42.01806410247894</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>84.09765999999999</v>
+        <v>82.45252000000001</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>88.08798</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>3.990320000000011</v>
+        <v>5.635459999999995</v>
       </c>
     </row>
     <row r="9">
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>402.43794206</v>
+        <v>611.75803042</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>439.5389236</v>
+        <v>514.5637450400001</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>-37.10098154000001</v>
+        <v>97.1942853799999</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-9.219056570582646</v>
+        <v>15.88770078151186</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>77.25902000000001</v>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>398.94096058</v>
+        <v>608.3930804399999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>439.5389236</v>
+        <v>514.5637450400001</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>-40.59796301999997</v>
+        <v>93.82933539999986</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-10.17643386654924</v>
+        <v>15.4224856292154</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>76.85171999999999</v>
@@ -1242,25 +1242,25 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>779.32355682</v>
+        <v>678.0726331799999</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>387.99922672</v>
+        <v>711.6739775000001</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>391.3243301</v>
+        <v>-33.60134432000015</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>50.21333266208248</v>
+        <v>-4.955419622587895</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>87.72114999999999</v>
+        <v>87.71088</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>73.89806000000002</v>
+        <v>94.87696</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>-13.82308999999998</v>
+        <v>7.166079999999994</v>
       </c>
     </row>
     <row r="12">
@@ -1272,25 +1272,25 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>380.1999963600001</v>
+        <v>725.6329613599999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>387.99922672</v>
+        <v>711.6739775000001</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>-7.799230359999987</v>
+        <v>13.9589838599998</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>-2.051349404173883</v>
+        <v>1.923697599656653</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>73.35805999999999</v>
+        <v>77.61855999999999</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>73.89806000000002</v>
+        <v>94.87696</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.5400000000000205</v>
+        <v>17.25840000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1302,25 +1302,25 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>379.02569662</v>
+        <v>733.6272137800001</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>387.99922672</v>
+        <v>711.6739775000001</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>-8.973530100000033</v>
+        <v>21.95323628000007</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-2.367525521362376</v>
+        <v>2.992423926981449</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>73.12326</v>
+        <v>77.50183999999999</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>73.89806000000002</v>
+        <v>94.87696</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.7748000000000133</v>
+        <v>17.37512000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Model_Comparison_Across_Networks.xlsx
+++ b/Model_Comparison_Across_Networks.xlsx
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>71.59054244000001</v>
+        <v>73.94904883999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>105.43504684</v>
+        <v>71.54982554</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>109.94782728</v>
+        <v>71.54982554</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
     </row>
     <row r="3">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>171.06750906</v>
+        <v>213.48660962</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>213.9586902200001</v>
+        <v>209.89549308</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>255.16770582</v>
+        <v>250.76989134</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>212.66504392</v>
+        <v>212.10658592</v>
       </c>
     </row>
     <row r="5">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>90.72194</v>
+        <v>91.2577</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>78.11203999999999</v>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>887.45526874</v>
+        <v>885.2719316199999</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>611.75803042</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>608.3930804399999</v>
+        <v>600.33723754</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>514.5637450400001</v>
+        <v>511.67817784</v>
       </c>
     </row>
     <row r="7">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>678.0726331799999</v>
+        <v>676.8887525199999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>725.6329613599999</v>
+        <v>714.7804355599999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>733.6272137800001</v>
+        <v>722.85542358</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>711.6739775000001</v>
+        <v>710.5593757999999</v>
       </c>
     </row>
     <row r="9">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>452.046488355</v>
+        <v>462.39908565</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>414.19618221</v>
+        <v>401.99594615</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>426.78395683</v>
+        <v>411.3780945</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>388.960994375</v>
+        <v>377.19835262</v>
       </c>
     </row>
     <row r="3">
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>88.14047000000001</v>
+        <v>90.328265</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>77.75139</v>
+        <v>83.247405</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>77.536315</v>
+        <v>82.96486999999999</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>93.14343</v>
+        <v>94.07298</v>
       </c>
     </row>
   </sheetData>
@@ -948,25 +948,25 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>71.59054244000001</v>
+        <v>73.94904883999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>-45.35066859999999</v>
+        <v>-0.5002220800000213</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>-63.3472900949289</v>
+        <v>-0.6764415335244243</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>4.605260000000001</v>
+        <v>0.1080400000000026</v>
       </c>
     </row>
     <row r="3">
@@ -978,25 +978,25 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>105.43504684</v>
+        <v>71.54982554</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>-11.50616419999998</v>
+        <v>-2.899445380000005</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-10.91303560329502</v>
+        <v>-4.052344444053279</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>18.26586</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1008,25 +1008,25 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>109.94782728</v>
+        <v>71.54982554</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>116.94121104</v>
+        <v>74.44927092</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>-6.993383759999997</v>
+        <v>-2.899445380000005</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-6.360638434618821</v>
+        <v>-4.052344444053279</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>17.99602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1046,25 +1046,25 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>171.06750906</v>
+        <v>213.48660962</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>212.66504392</v>
+        <v>212.10658592</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>-41.59753486000002</v>
+        <v>1.38002370000002</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-24.31644389315925</v>
+        <v>0.6464216666592917</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>90.72194</v>
+        <v>91.2577</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>93.32698000000001</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>2.605040000000002</v>
+        <v>2.069280000000006</v>
       </c>
     </row>
     <row r="6">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>213.9586902200001</v>
+        <v>209.89549308</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>212.66504392</v>
+        <v>212.10658592</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>1.293646300000022</v>
+        <v>-2.211092839999997</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.6046243312995833</v>
+        <v>-1.053425591733529</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>78.11203999999999</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>255.16770582</v>
+        <v>250.76989134</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>212.66504392</v>
+        <v>212.10658592</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>42.50266189999995</v>
+        <v>38.66330542000002</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>16.65675590232493</v>
+        <v>15.4178419161092</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>77.50592</v>
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>887.45526874</v>
+        <v>885.2719316199999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>514.5637450400001</v>
+        <v>511.67817784</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>372.8915236999999</v>
+        <v>373.5937537799999</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>42.01806410247894</v>
+        <v>42.20101648273695</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>82.45252000000001</v>
@@ -1177,13 +1177,13 @@
         <v>611.75803042</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>514.5637450400001</v>
+        <v>511.67817784</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>97.1942853799999</v>
+        <v>100.07985258</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>15.88770078151186</v>
+        <v>16.35938518229022</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>77.25902000000001</v>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>608.3930804399999</v>
+        <v>600.33723754</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>514.5637450400001</v>
+        <v>511.67817784</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>93.82933539999986</v>
+        <v>88.65905969999999</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>15.4224856292154</v>
+        <v>14.76820929238005</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>76.85171999999999</v>
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>678.0726331799999</v>
+        <v>676.8887525199999</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>711.6739775000001</v>
+        <v>710.5593757999999</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>-33.60134432000015</v>
+        <v>-33.67062328000006</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-4.955419622587895</v>
+        <v>-4.974321578641566</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>87.71088</v>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>725.6329613599999</v>
+        <v>714.7804355599999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>711.6739775000001</v>
+        <v>710.5593757999999</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>13.9589838599998</v>
+        <v>4.221059759999974</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1.923697599656653</v>
+        <v>0.5905393530662258</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>77.61855999999999</v>
@@ -1302,16 +1302,16 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>733.6272137800001</v>
+        <v>722.85542358</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>711.6739775000001</v>
+        <v>710.5593757999999</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>21.95323628000007</v>
+        <v>12.29604778000002</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>2.992423926981449</v>
+        <v>1.701038323694502</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>77.50183999999999</v>
